--- a/artfynd/A 40002-2025 artfynd.xlsx
+++ b/artfynd/A 40002-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,12 +678,7 @@
         <v>112251043</v>
       </c>
       <c r="B2" t="n">
-        <v>90898</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93223</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -700,12 +695,12 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Phellodon connatus</t>
+          <t>Phellodon melaleucus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Schultz) nom.prov</t>
+          <t>(Sw. ex Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -797,6 +792,120 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>93638708</v>
+      </c>
+      <c r="B3" t="n">
+        <v>57144</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>102613</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Orre</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Lyrurus tetrix</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Östjuten, södra viken vid rastplats, Ög</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>552964</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6516061</v>
+      </c>
+      <c r="S3" t="n">
+        <v>50</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Finspång</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Risinge</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2021-05-03</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2021-05-03</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>På vägen.</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Ulrika Granroth</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Ulrika Granroth</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 40002-2025 artfynd.xlsx
+++ b/artfynd/A 40002-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AZ3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -792,6 +797,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112251043</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -906,8 +916,17 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/93638708</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>